--- a/ESTP/BMC2/S4/Exam2/NotesBMC2Exam2.xlsx
+++ b/ESTP/BMC2/S4/Exam2/NotesBMC2Exam2.xlsx
@@ -1,31 +1,42 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://entestp-my.sharepoint.com/personal/mberger_estp_fr/Documents/Documents/Projets/slides/ESTP/BMC2/S4/Exam2/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="55" documentId="11_F25DC773A252ABDACC1048FAE91D44005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{427BEDF2-C0A3-406D-A6A5-A8EC0D59FA34}"/>
+  <xr:revisionPtr revIDLastSave="192" documentId="11_F25DC773A252ABDACC1048FAE91D44005BDE58EE" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{323B823D-69A4-4943-9468-DA5F5FFE6D67}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-24900" yWindow="3315" windowWidth="21705" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="32" uniqueCount="32">
   <si>
     <t>GANE</t>
   </si>
@@ -118,6 +129,9 @@
   </si>
   <si>
     <t>Exo 3.1</t>
+  </si>
+  <si>
+    <t>sur 20</t>
   </si>
 </sst>
 </file>
@@ -133,15 +147,21 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -179,14 +199,28 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -467,271 +501,689 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A6:N20"/>
+  <dimension ref="A6:P21"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.06640625" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="2" width="15.9296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="C6" t="s">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="D6" t="s">
         <v>28</v>
       </c>
-      <c r="D6">
-        <v>2</v>
-      </c>
       <c r="E6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>4</v>
-      </c>
-      <c r="G6" t="s">
+        <v>3</v>
+      </c>
+      <c r="G6" s="5">
+        <v>4</v>
+      </c>
+      <c r="H6" t="s">
         <v>29</v>
       </c>
-      <c r="H6">
-        <v>2</v>
-      </c>
       <c r="I6">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="J6">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K6">
+        <v>4</v>
+      </c>
+      <c r="L6" s="5">
         <v>5</v>
       </c>
-      <c r="L6" t="s">
+      <c r="M6" t="s">
         <v>30</v>
       </c>
-      <c r="M6">
-        <v>2</v>
-      </c>
       <c r="N6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="O6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="C7" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+      <c r="F7">
+        <v>2</v>
+      </c>
+      <c r="G7" s="5">
+        <v>3</v>
+      </c>
+      <c r="H7">
+        <v>2</v>
+      </c>
+      <c r="I7">
+        <v>3</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="K7">
+        <v>2</v>
+      </c>
+      <c r="L7" s="5">
+        <v>2</v>
+      </c>
+      <c r="M7">
+        <v>4</v>
+      </c>
+      <c r="N7">
+        <v>4</v>
+      </c>
+      <c r="O7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A8" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C7">
-        <v>4</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-      <c r="E7">
-        <v>4</v>
-      </c>
-      <c r="G7">
-        <v>4</v>
-      </c>
-      <c r="H7">
-        <v>4</v>
-      </c>
-      <c r="L7">
-        <v>4</v>
-      </c>
-      <c r="M7">
-        <v>1</v>
-      </c>
-      <c r="N7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A8" s="1" t="s">
-        <v>2</v>
-      </c>
       <c r="B8" s="1" t="s">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="C8">
-        <v>4</v>
+        <f>ROUNDUP(P8*20/30,1)</f>
+        <v>12.7</v>
       </c>
       <c r="D8">
         <v>4</v>
       </c>
-      <c r="G8">
-        <v>4</v>
-      </c>
+      <c r="E8">
+        <v>4</v>
+      </c>
+      <c r="F8">
+        <v>4</v>
+      </c>
+      <c r="G8" s="5"/>
       <c r="H8">
-        <v>3</v>
-      </c>
-      <c r="L8">
-        <v>3</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>4</v>
+      </c>
+      <c r="J8">
+        <v>0</v>
+      </c>
+      <c r="L8" s="5"/>
       <c r="M8">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.45">
+        <v>4</v>
+      </c>
+      <c r="N8">
+        <v>1</v>
+      </c>
+      <c r="O8">
+        <v>4</v>
+      </c>
+      <c r="P8">
+        <f>SUMPRODUCT(D8:O8,D$7:O$7)/4</f>
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:16" x14ac:dyDescent="0.45">
       <c r="A9" s="1" t="s">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B9" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C9">
+        <f>ROUNDUP(P9*20/30,1)</f>
+        <v>12.4</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+      <c r="E9">
+        <v>4</v>
+      </c>
+      <c r="F9">
+        <v>4</v>
+      </c>
+      <c r="G9" s="5">
+        <v>3</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>3</v>
+      </c>
+      <c r="L9" s="5"/>
+      <c r="M9">
+        <v>3</v>
+      </c>
+      <c r="N9">
+        <v>2</v>
+      </c>
+      <c r="P9">
+        <f t="shared" ref="P9:P21" si="0">SUMPRODUCT(D9:O9,D$7:O$7)/4</f>
+        <v>18.5</v>
+      </c>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A10" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C9">
-        <v>4</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>4</v>
-      </c>
-      <c r="G9">
-        <v>4</v>
-      </c>
-      <c r="H9">
-        <v>3</v>
-      </c>
-      <c r="I9">
-        <v>1</v>
-      </c>
-      <c r="J9">
-        <v>2</v>
-      </c>
-      <c r="K9">
-        <v>2</v>
-      </c>
-      <c r="L9">
-        <v>4</v>
-      </c>
-      <c r="M9">
-        <v>3</v>
-      </c>
-      <c r="N9">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A10" s="1" t="s">
+      <c r="C10">
+        <f>ROUNDUP(P10*20/30,1)</f>
+        <v>19</v>
+      </c>
+      <c r="D10">
+        <v>4</v>
+      </c>
+      <c r="E10">
+        <v>4</v>
+      </c>
+      <c r="F10">
+        <v>4</v>
+      </c>
+      <c r="G10" s="5">
+        <v>4</v>
+      </c>
+      <c r="H10">
+        <v>4</v>
+      </c>
+      <c r="I10">
+        <v>4</v>
+      </c>
+      <c r="J10">
+        <v>4</v>
+      </c>
+      <c r="K10">
+        <v>4</v>
+      </c>
+      <c r="L10" s="5">
+        <v>2</v>
+      </c>
+      <c r="M10">
+        <v>4</v>
+      </c>
+      <c r="N10">
+        <v>4</v>
+      </c>
+      <c r="O10">
+        <v>3</v>
+      </c>
+      <c r="P10">
+        <f t="shared" si="0"/>
+        <v>28.5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="1" t="s">
+      <c r="B11" s="1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A11" s="1" t="s">
+      <c r="C11">
+        <f>ROUNDUP(P11*20/30,1)</f>
+        <v>9.9</v>
+      </c>
+      <c r="D11">
+        <v>4</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11" s="5">
+        <v>1</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>4</v>
+      </c>
+      <c r="J11">
+        <v>2</v>
+      </c>
+      <c r="K11">
+        <v>1</v>
+      </c>
+      <c r="L11" s="5"/>
+      <c r="M11">
+        <v>2</v>
+      </c>
+      <c r="O11">
+        <v>0</v>
+      </c>
+      <c r="P11">
+        <f t="shared" si="0"/>
+        <v>14.75</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="B12" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C11">
-        <v>4</v>
-      </c>
-      <c r="D11">
-        <v>4</v>
-      </c>
-      <c r="E11">
-        <v>4</v>
-      </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="G11">
-        <v>4</v>
-      </c>
-      <c r="H11">
-        <v>4</v>
-      </c>
-      <c r="I11">
-        <v>4</v>
-      </c>
-      <c r="K11">
-        <v>2</v>
-      </c>
-      <c r="L11">
-        <v>4</v>
-      </c>
-      <c r="M11">
-        <v>2</v>
-      </c>
-      <c r="N11">
+      <c r="C12">
+        <f>ROUNDUP(P12*20/30,1)</f>
+        <v>15.4</v>
+      </c>
+      <c r="D12" s="4">
+        <v>4</v>
+      </c>
+      <c r="E12" s="4">
+        <v>4</v>
+      </c>
+      <c r="F12" s="4">
+        <v>4</v>
+      </c>
+      <c r="G12" s="6">
+        <v>4</v>
+      </c>
+      <c r="H12" s="4">
+        <v>4</v>
+      </c>
+      <c r="I12" s="4">
+        <v>4</v>
+      </c>
+      <c r="J12" s="4">
+        <v>4</v>
+      </c>
+      <c r="L12" s="6">
+        <v>2</v>
+      </c>
+      <c r="M12" s="4">
+        <v>4</v>
+      </c>
+      <c r="N12" s="4">
+        <v>2</v>
+      </c>
+      <c r="O12" s="4">
         <v>0</v>
       </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A12" s="1" t="s">
+      <c r="P12">
+        <f t="shared" si="0"/>
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="B12" s="1" t="s">
+      <c r="B13" s="1" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A13" s="1" t="s">
+      <c r="C13">
+        <f>ROUNDUP(P13*20/30,1)</f>
+        <v>8.4</v>
+      </c>
+      <c r="D13">
+        <v>4</v>
+      </c>
+      <c r="E13">
+        <v>4</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" s="5"/>
+      <c r="H13">
+        <v>4</v>
+      </c>
+      <c r="I13">
+        <v>4</v>
+      </c>
+      <c r="J13">
+        <v>4</v>
+      </c>
+      <c r="L13" s="5"/>
+      <c r="M13">
+        <v>1</v>
+      </c>
+      <c r="P13">
+        <f t="shared" si="0"/>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A14" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B14" s="1" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A14" s="1" t="s">
+      <c r="C14">
+        <f>ROUNDUP(P14*20/30,1)</f>
+        <v>16.700000000000003</v>
+      </c>
+      <c r="D14">
+        <v>4</v>
+      </c>
+      <c r="E14">
+        <v>4</v>
+      </c>
+      <c r="F14">
+        <v>4</v>
+      </c>
+      <c r="G14" s="5">
+        <v>2</v>
+      </c>
+      <c r="H14" s="7">
+        <v>4</v>
+      </c>
+      <c r="I14" s="7">
+        <v>4</v>
+      </c>
+      <c r="J14" s="7">
+        <v>4</v>
+      </c>
+      <c r="L14" s="5">
+        <v>1</v>
+      </c>
+      <c r="M14">
+        <v>4</v>
+      </c>
+      <c r="N14">
+        <v>4</v>
+      </c>
+      <c r="O14">
+        <v>4</v>
+      </c>
+      <c r="P14">
+        <f t="shared" si="0"/>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A15" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A15" s="1" t="s">
+      <c r="C15">
+        <f>ROUNDUP(P15*20/30,1)</f>
+        <v>15</v>
+      </c>
+      <c r="D15">
+        <v>4</v>
+      </c>
+      <c r="E15">
+        <v>4</v>
+      </c>
+      <c r="F15">
+        <v>4</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0</v>
+      </c>
+      <c r="H15">
+        <v>4</v>
+      </c>
+      <c r="I15">
+        <v>4</v>
+      </c>
+      <c r="J15">
+        <v>2</v>
+      </c>
+      <c r="K15">
+        <v>4</v>
+      </c>
+      <c r="L15" s="5">
+        <v>4</v>
+      </c>
+      <c r="M15">
+        <v>4</v>
+      </c>
+      <c r="N15">
+        <v>2</v>
+      </c>
+      <c r="P15">
+        <f t="shared" si="0"/>
+        <v>22.5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A16" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B15" s="1" t="s">
+      <c r="B16" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.45">
-      <c r="A16" s="1" t="s">
+      <c r="C16">
+        <f>ROUNDUP(P16*20/30,1)</f>
+        <v>12</v>
+      </c>
+      <c r="D16">
+        <v>4</v>
+      </c>
+      <c r="E16">
+        <v>3</v>
+      </c>
+      <c r="F16">
+        <v>4</v>
+      </c>
+      <c r="G16" s="5">
+        <v>4</v>
+      </c>
+      <c r="H16">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <v>4</v>
+      </c>
+      <c r="L16" s="5"/>
+      <c r="M16">
+        <v>3</v>
+      </c>
+      <c r="N16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <f t="shared" si="0"/>
         <v>18</v>
       </c>
-      <c r="B16" s="1" t="s">
+    </row>
+    <row r="17" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A17" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="B17" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A17" s="1" t="s">
+      <c r="C17">
+        <f>ROUNDUP(P17*20/30,1)</f>
+        <v>13.5</v>
+      </c>
+      <c r="D17">
+        <v>4</v>
+      </c>
+      <c r="E17">
+        <v>4</v>
+      </c>
+      <c r="F17">
+        <v>4</v>
+      </c>
+      <c r="G17" s="5">
+        <v>4</v>
+      </c>
+      <c r="H17">
+        <v>4</v>
+      </c>
+      <c r="I17">
+        <v>3</v>
+      </c>
+      <c r="J17">
+        <v>4</v>
+      </c>
+      <c r="L17" s="5"/>
+      <c r="M17">
+        <v>4</v>
+      </c>
+      <c r="N17">
+        <v>1</v>
+      </c>
+      <c r="P17">
+        <f t="shared" si="0"/>
+        <v>20.25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:16" s="4" customFormat="1" ht="13.9" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B17" s="1" t="s">
+      <c r="B18" s="3" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A18" s="1" t="s">
+      <c r="C18">
+        <f>ROUNDUP(P18*20/30,1)</f>
+        <v>0</v>
+      </c>
+      <c r="G18" s="6"/>
+      <c r="L18" s="6"/>
+      <c r="P18">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A19" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="B18" s="1" t="s">
+      <c r="B19" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A19" s="1" t="s">
+      <c r="C19">
+        <f>ROUNDUP(P19*20/30,1)</f>
+        <v>13.7</v>
+      </c>
+      <c r="D19">
+        <v>2</v>
+      </c>
+      <c r="E19">
+        <v>2</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+      <c r="G19" s="5">
+        <v>2</v>
+      </c>
+      <c r="H19">
+        <v>4</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="J19">
+        <v>4</v>
+      </c>
+      <c r="K19">
+        <v>0</v>
+      </c>
+      <c r="L19" s="5">
+        <v>2</v>
+      </c>
+      <c r="M19">
+        <v>4</v>
+      </c>
+      <c r="N19">
+        <v>4</v>
+      </c>
+      <c r="O19">
+        <v>1</v>
+      </c>
+      <c r="P19">
+        <f t="shared" si="0"/>
+        <v>20.5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A20" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="B19" s="1" t="s">
+      <c r="B20" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A20" s="2" t="s">
+      <c r="C20">
+        <f>ROUNDUP(P20*20/30,1)</f>
+        <v>11.5</v>
+      </c>
+      <c r="D20">
+        <v>4</v>
+      </c>
+      <c r="E20">
+        <v>4</v>
+      </c>
+      <c r="F20">
+        <v>4</v>
+      </c>
+      <c r="G20" s="5">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>4</v>
+      </c>
+      <c r="I20">
+        <v>4</v>
+      </c>
+      <c r="L20" s="5"/>
+      <c r="M20">
+        <v>3</v>
+      </c>
+      <c r="P20">
+        <f t="shared" si="0"/>
+        <v>17.25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:16" x14ac:dyDescent="0.45">
+      <c r="A21" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B20" s="2" t="s">
+      <c r="B21" s="2" t="s">
         <v>27</v>
+      </c>
+      <c r="C21">
+        <f>ROUNDUP(P21*20/30,1)</f>
+        <v>3.7</v>
+      </c>
+      <c r="G21" s="5"/>
+      <c r="H21">
+        <v>3</v>
+      </c>
+      <c r="I21">
+        <v>1</v>
+      </c>
+      <c r="J21">
+        <v>1</v>
+      </c>
+      <c r="L21" s="5"/>
+      <c r="M21">
+        <v>3</v>
+      </c>
+      <c r="N21">
+        <v>0</v>
+      </c>
+      <c r="O21">
+        <v>0</v>
+      </c>
+      <c r="P21">
+        <f t="shared" si="0"/>
+        <v>5.5</v>
       </c>
     </row>
   </sheetData>
